--- a/artfynd/A 44514-2024 artfynd.xlsx
+++ b/artfynd/A 44514-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69300119</v>
+        <v>69300118</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528549.0902737665</v>
+        <v>528484</v>
       </c>
       <c r="R2" t="n">
-        <v>6987556.038601288</v>
+        <v>6987618</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,12 +764,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -792,7 +777,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # Sälg # Salix caprea</t>
+          <t>1 substratenheter # Grov, murken tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,37 +795,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69300123</v>
+        <v>69300119</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528337.8611353879</v>
+        <v>528549</v>
       </c>
       <c r="R3" t="n">
-        <v>6987580.079318861</v>
+        <v>6987556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,15 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69300120</v>
+        <v>69300117</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -985,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528337.8611353879</v>
+        <v>528484</v>
       </c>
       <c r="R4" t="n">
-        <v>6987580.079318861</v>
+        <v>6987618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,21 +983,11 @@
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1049,12 +1004,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1062,7 +1017,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # Sälg # Salix caprea</t>
+          <t>1 substratenheter # Brandhögstubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,37 +1035,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69300124</v>
+        <v>69300125</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1120,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528265.0638252909</v>
+        <v>528288</v>
       </c>
       <c r="R5" t="n">
-        <v>6987479.077564015</v>
+        <v>6987451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,21 +1103,11 @@
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1184,20 +1124,20 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2 substratenheter # Asp # Populus tremula</t>
+          <t>1 substratenheter # Brandhögstubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1215,37 +1155,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69300118</v>
+        <v>69300124</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1255,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528483.9674015783</v>
+        <v>528265</v>
       </c>
       <c r="R6" t="n">
-        <v>6987618.140695805</v>
+        <v>6987479</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,21 +1223,11 @@
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1319,20 +1244,20 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # Grov, murken tallåga # Pinus sylvestris</t>
+          <t>2 substratenheter # Asp # Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1350,37 +1275,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69300122</v>
+        <v>69300120</v>
       </c>
       <c r="B7" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1390,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528337.8611353879</v>
+        <v>528338</v>
       </c>
       <c r="R7" t="n">
-        <v>6987580.079318861</v>
+        <v>6987580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,19 +1343,9 @@
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-10-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,37 +1395,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69300117</v>
+        <v>69300123</v>
       </c>
       <c r="B8" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1525,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528483.9674015783</v>
+        <v>528338</v>
       </c>
       <c r="R8" t="n">
-        <v>6987618.140695805</v>
+        <v>6987580</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1558,21 +1463,11 @@
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-10-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1589,12 +1484,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1602,7 +1497,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # Brandhögstubbe # Pinus sylvestris</t>
+          <t>1 substratenheter # Sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1617,6 +1512,126 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>69300122</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>528338</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6987580</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-10-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-10-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Sälg # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44514-2024 artfynd.xlsx
+++ b/artfynd/A 44514-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300119</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300117</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300125</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300124</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,6 +1422,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300120</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1512,6 +1547,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300123</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1632,8 +1672,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300122</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>